--- a/notebooks/01_first_analysis/table_5_5_stability.xlsx
+++ b/notebooks/01_first_analysis/table_5_5_stability.xlsx
@@ -458,100 +458,100 @@
         <v>50.157</v>
       </c>
       <c r="D2" t="n">
-        <v>0.278</v>
+        <v>0.27</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7</v>
+        <v>0.735</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Claude Sonnet 4.6</t>
+          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Group 2: Foundation Models</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.289</v>
+        <v>50.644</v>
       </c>
       <c r="D3" t="n">
-        <v>0.308</v>
+        <v>0.284</v>
       </c>
       <c r="E3" t="n">
-        <v>0.396</v>
+        <v>0.652</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Modelo_Qwen3.5_9B</t>
+          <t>Claude Sonnet 4.6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Group 3: UNE Standard</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44.697</v>
+        <v>50.289</v>
       </c>
       <c r="D4" t="n">
-        <v>0.318</v>
+        <v>0.31</v>
       </c>
       <c r="E4" t="n">
-        <v>0.509</v>
+        <v>0.497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Asistente Lectura Facilitada "Francisco Javier Alvarez Jimenez"</t>
+          <t>deepseek-v3.2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Group 1: Conversational Agents</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.644</v>
+        <v>53.376</v>
       </c>
       <c r="D5" t="n">
-        <v>0.319</v>
+        <v>0.334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.672</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Placea</t>
+          <t>Modelo_Qwen3.5_9B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Group 1: Conversational Agents</t>
+          <t>Group 3: UNE Standard</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>42.196</v>
+        <v>44.697</v>
       </c>
       <c r="D6" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="E6" t="n">
-        <v>0.471</v>
+        <v>0.459</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
+          <t>Placea</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -560,97 +560,97 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47.261</v>
+        <v>42.196</v>
       </c>
       <c r="D7" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="E7" t="n">
-        <v>0.536</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>deepseek-v3.2</t>
+          <t xml:space="preserve">Asistente de lectura fácil “Mark Jonathan Camacho Escatel”: </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Group 2: Foundation Models</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53.376</v>
+        <v>47.261</v>
       </c>
       <c r="D8" t="n">
-        <v>0.369</v>
+        <v>0.356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.672</v>
+        <v>0.5669999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SimpleText (ClearText)</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Group 3: UNE Standard</t>
+          <t>Group 2: Foundation Models</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.079</v>
+        <v>49.305</v>
       </c>
       <c r="D9" t="n">
-        <v>0.37</v>
+        <v>0.367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.594</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gemini 3.1 Pro</t>
+          <t>Asistente de lectura fácil “Antonio Gonzales Crespo”</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Group 2: Foundation Models</t>
+          <t>Group 1: Conversational Agents</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>49.305</v>
+        <v>46.722</v>
       </c>
       <c r="D10" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="E10" t="n">
-        <v>0.455</v>
+        <v>0.515</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Asistente de lectura fácil “Antonio Gonzales Crespo”</t>
+          <t>SimpleText (ClearText)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Group 1: Conversational Agents</t>
+          <t>Group 3: UNE Standard</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.722</v>
+        <v>41.079</v>
       </c>
       <c r="D11" t="n">
-        <v>0.386</v>
+        <v>0.413</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="12">
@@ -668,10 +668,10 @@
         <v>39.662</v>
       </c>
       <c r="D12" t="n">
-        <v>0.437</v>
+        <v>0.455</v>
       </c>
       <c r="E12" t="n">
-        <v>0.521</v>
+        <v>0.505</v>
       </c>
     </row>
   </sheetData>
